--- a/WIP/月茗/LAN阿斯特莱雅/新建 XLSX 工作表.xlsx
+++ b/WIP/月茗/LAN阿斯特莱雅/新建 XLSX 工作表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19395" windowHeight="17655"/>
+    <workbookView windowWidth="28755" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>名称</t>
   </si>
@@ -94,6 +94,13 @@
     <t>重组王宫骑士团</t>
   </si>
   <si>
+    <t>“阿斯特莱雅皇家陆军”追加效果：
+特种攻击-5%，特种防御-5%
+启用总司令：克里斯蒂娜·摩根（特种部队-奇才）
+1*100%加成：特种部队
+在首都地区部署三个王宫骑士团师</t>
+  </si>
+  <si>
     <t>安艺真琴的提案</t>
   </si>
   <si>
@@ -104,6 +111,11 @@
     <t>精简动员流程</t>
   </si>
   <si>
+    <t>人力+10000
+“阿斯特莱雅皇家陆军”追加效果：
+征兵法案-10%，适役人口修正+10%</t>
+  </si>
+  <si>
     <t>利用缴获装备</t>
   </si>
   <si>
@@ -120,21 +132,37 @@
     <t>战争部</t>
   </si>
   <si>
+    <t>获得“战争部”（计划上限+10%，动员速度+5%）</t>
+  </si>
+  <si>
     <t>战争源泉</t>
   </si>
   <si>
     <t>民主兵工厂</t>
   </si>
   <si>
+    <t>随机 3 个地区添加 2 军用工厂</t>
+  </si>
+  <si>
     <t>美波铃奈的提案</t>
   </si>
   <si>
+    <t>1*75%花费减少：陆军学说
+为装甲子路线添加精通度</t>
+  </si>
+  <si>
     <t>改进通讯设备</t>
   </si>
   <si>
+    <t>1*100%加成：电子设备</t>
+  </si>
+  <si>
     <t>新式装甲研发</t>
   </si>
   <si>
+    <t>1*100%加成：中型坦克</t>
+  </si>
+  <si>
     <t>前线指挥</t>
   </si>
   <si>
@@ -147,10 +175,18 @@
     <t>规范化后勤体系</t>
   </si>
   <si>
+    <t>“阿斯特莱雅皇家陆军”追加效果：
+补给消耗-15%，陆军燃料消耗-10%</t>
+  </si>
+  <si>
     <t>勇攀新高峰</t>
   </si>
   <si>
     <t>一号命令</t>
+  </si>
+  <si>
+    <t>1*75%花费减少：陆军学说
+为作战子路线添加精通度</t>
   </si>
   <si>
     <t>组建实验部队</t>
@@ -811,7 +847,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -822,22 +858,19 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -954,7 +987,7 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>2009775</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -972,7 +1005,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9363075" y="4248150"/>
+          <a:off x="9363075" y="5105400"/>
           <a:ext cx="1981200" cy="1171575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -996,7 +1029,7 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>2057400</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1014,7 +1047,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9315450" y="5829300"/>
+          <a:off x="9315450" y="7372350"/>
           <a:ext cx="2076450" cy="1695450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1299,7 +1332,7 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1307,7 +1340,7 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1327,7 +1360,7 @@
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1352,167 +1385,190 @@
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="8"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" ht="81" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" ht="27" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" ht="40.5" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="27" spans="1:4">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" ht="27" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="8"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>28</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="27" spans="1:4">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="7" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
-      <c r="D19" s="8"/>
+      <c r="D19" s="7" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
-      <c r="D21" s="8"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" ht="27" spans="1:4">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
-      <c r="D23" s="8"/>
+      <c r="D23" s="7" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" ht="27" spans="1:4">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
-      <c r="D25" s="8"/>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="8"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="8"/>
+      <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="8"/>
+      <c r="D31" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
